--- a/activities/activity-11-prepare-a-gst-control-and-f5-working-paper/activity-11-control.xlsx
+++ b/activities/activity-11-prepare-a-gst-control-and-f5-working-paper/activity-11-control.xlsx
@@ -712,11 +712,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="25505867"/>
-        <c:axId val="27789068"/>
+        <c:axId val="48642868"/>
+        <c:axId val="32377221"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25505867"/>
+        <c:axId val="48642868"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,7 +749,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27789068"/>
+        <c:crossAx val="32377221"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -757,7 +757,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27789068"/>
+        <c:axId val="32377221"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -833,7 +833,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25505867"/>
+        <c:crossAx val="48642868"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
